--- a/GeekBrains/Lesson_5-The_history_of_the_git_project/5_Commands.xlsx
+++ b/GeekBrains/Lesson_5-The_history_of_the_git_project/5_Commands.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\GeekBrains\Lesson 5. The history of the git project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\GeekBrains\Lesson_5-The_history_of_the_git_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448F9365-AEC4-4F5A-8BA2-E0CCAA5774C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EE5297-E435-478B-9BBC-59EBAE2B8E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -479,7 +479,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -487,7 +487,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
